--- a/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0002T0006Z000C1N36_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0002T0006Z000C1N36_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>92.66033199563323</v>
+        <v>15.0573039492904</v>
       </c>
       <c r="D2" t="n">
-        <v>91.7764216447657</v>
+        <v>14.91366851727443</v>
       </c>
       <c r="E2" t="n">
-        <v>32.06339061972973</v>
+        <v>5.210300975706081</v>
       </c>
       <c r="F2" t="n">
-        <v>32.13332228786632</v>
+        <v>5.221664871778277</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>93.13180196085875</v>
+        <v>15.13391781863955</v>
       </c>
       <c r="D3" t="n">
-        <v>92.40585304375632</v>
+        <v>15.0159511196104</v>
       </c>
       <c r="E3" t="n">
-        <v>32.06339061972973</v>
+        <v>5.210300975706081</v>
       </c>
       <c r="F3" t="n">
-        <v>32.13332228786632</v>
+        <v>5.221664871778277</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>90.99642080213938</v>
+        <v>14.78691838034765</v>
       </c>
       <c r="D4" t="n">
-        <v>90.44102929653667</v>
+        <v>14.69666726068721</v>
       </c>
       <c r="E4" t="n">
-        <v>32.06339061972973</v>
+        <v>5.210300975706081</v>
       </c>
       <c r="F4" t="n">
-        <v>32.13332228786632</v>
+        <v>5.221664871778277</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>94.19892688348126</v>
+        <v>15.30732561856571</v>
       </c>
       <c r="D5" t="n">
-        <v>94.11071509123154</v>
+        <v>15.29299120232513</v>
       </c>
       <c r="E5" t="n">
-        <v>32.06339061972973</v>
+        <v>5.210300975706081</v>
       </c>
       <c r="F5" t="n">
-        <v>32.13332228786632</v>
+        <v>5.221664871778277</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>61.03385198262747</v>
+        <v>9.918000947176964</v>
       </c>
       <c r="D6" t="n">
-        <v>60.01066452108036</v>
+        <v>9.751732984675559</v>
       </c>
       <c r="E6" t="n">
-        <v>32.06339061972973</v>
+        <v>5.210300975706081</v>
       </c>
       <c r="F6" t="n">
-        <v>32.13332228786632</v>
+        <v>5.221664871778277</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>3.525285451199937</v>
+        <v>0.5728588858199898</v>
       </c>
       <c r="D7" t="n">
-        <v>2.906249906882746</v>
+        <v>0.4722656098684462</v>
       </c>
       <c r="E7" t="n">
-        <v>32.06339061972973</v>
+        <v>5.210300975706081</v>
       </c>
       <c r="F7" t="n">
-        <v>32.13332228786632</v>
+        <v>5.221664871778277</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>44.79136351718259</v>
+        <v>7.278596571542171</v>
       </c>
       <c r="D8" t="n">
-        <v>43.90597697294444</v>
+        <v>7.134721258103473</v>
       </c>
       <c r="E8" t="n">
-        <v>32.06339061972973</v>
+        <v>5.210300975706081</v>
       </c>
       <c r="F8" t="n">
-        <v>32.13332228786632</v>
+        <v>5.221664871778277</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
